--- a/contracts-aresbank-s-a-a28386191 (8).xlsx
+++ b/contracts-aresbank-s-a-a28386191 (8).xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Apellidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Correo electrónico</t>
+    <t xml:space="preserve">email</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de la versión del contrato (dd/mm/yyyy)</t>
